--- a/test_support/fixtures/xlsx/xlsx-format-bracket.xlsx
+++ b/test_support/fixtures/xlsx/xlsx-format-bracket.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Word Project\test_support\fixtures\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D908230-E86F-4EEE-9F3D-DC5E1072E010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B23A730B-38E3-481E-BA6D-DAECAF9B446F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,6 +26,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="[Red]0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -62,8 +65,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -348,7 +352,7 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1">
+      <c r="A1" s="1">
         <v>44927</v>
       </c>
     </row>
